--- a/bizconfig/static-xlsx/moba/pixel_moba/item.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>是否消耗(用一次消失)</t>
+          <t>是否消耗(true/false)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -816,101 +816,1357 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7011</v>
+        <v>7003</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>longsword</t>
+          <t>ward</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>长剑</t>
+          <t>视野守卫</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>physical_attack=15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>res://gameplay/content/items/longsword/icon.png</t>
+          <t>res://gameplay/content/items/ward/icon.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>7004</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>elixer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>精华药剂</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/elixer/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>7012</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>boots</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>速度之靴</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>boots</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>300</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>move_speed=45</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>move_speed_pct=0.15</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>res://gameplay/content/items/boots/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7013</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>berserkers_greaves</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>狂战士胫甲</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>move_speed_pct=0.2;physical_attack=10</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/berserkers_greaves/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7011</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>longsword</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>长剑</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>350</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>physical_attack=15</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/longsword/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pickaxe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>十字镐</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>875</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>physical_attack=25</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/pickaxe/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bf_sword</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B.F.大剑</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>physical_attack=40</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/bf_sword/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cloak_of_agility</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>灵风斗篷</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>800</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>crit_rate=0.15</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/cloak_of_agility/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>phantom_dancer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>幻影之舞</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>900</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>physical_attack=30;crit_rate=0.15;move_speed_pct=0.05</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/phantom_dancer/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>infinity_edge</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>无尽之刃</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>physical_attack=70;crit_rate=0.2;crit_damage=0.5</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/infinity_edge/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7031</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>amplifying_tome</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>增幅法典</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>435</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>magic_attack=20</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/amplifying_tome/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7032</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>needlessly_large_rod</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>无用大棒</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>magic_attack=60</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/needlessly_large_rod/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7033</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lost_chapter</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>失落章节</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>magic_attack=40;max_mana=300</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/lost_chapter/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7034</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rabadons</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>死亡之帽</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>magic_attack=120</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/rabadons/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7035</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>void_staff</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>虚空之杖</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1365</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>magic_attack=70;max_mana=200</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/void_staff/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7041</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cloth_armor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>布甲</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>physical_defense=15</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/cloth_armor/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7042</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>chain_vest</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>锁子甲</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>800</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>physical_defense=40</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/chain_vest/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7043</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>negatron_cloak</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>负极斗篷</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>450</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>magic_defense=25</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/negatron_cloak/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7044</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>thornmail</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>荆棘之甲</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>physical_defense=60</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/thornmail/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7045</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>spirit_visage</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>振奋盔甲</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>magic_defense=40;hp_regen=5</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/spirit_visage/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7051</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>doran_blade</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>多兰之刃</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>450</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>physical_attack=8;max_hp=80</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/doran_blade/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7052</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>doran_ring</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>多兰之戒</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>450</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>magic_attack=15;max_mana=50;mana_regen=3</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/doran_ring/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7053</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>doran_shield</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>多兰之盾</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>450</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>max_hp=80;hp_regen=5</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/doran_shield/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wardstone</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>守卫石</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>800</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>max_hp=50</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/wardstone/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7061</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>trinity_force</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>三相之力</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3733</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>physical_attack=25;max_hp=250;max_mana=250;move_speed_pct=0.05;crit_rate=0.2</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/trinity_force/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7062</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>guardian_angel</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>守护天使</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>physical_defense=40;magic_defense=40</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/guardian_angel/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7063</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>last_whisper</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>最后的轻语</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>physical_attack=35</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/last_whisper/icon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7064</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>liandrys</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>里兰的折磨</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>magic_attack=75;max_hp=300</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/items/liandrys/icon.png</t>
         </is>
       </c>
     </row>
